--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,32 +538,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Myanmar National League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ispe FC x Dagon FC</t>
+          <t>Qingdao Hainiu x Beijing Guoan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ispe FC</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dagon FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -595,21 +595,185 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>730</v>
+        <v>564</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>200</v>
       </c>
       <c r="S2" t="n">
-        <v>34.48</v>
+        <v>29.41</v>
       </c>
       <c r="T2" t="n">
-        <v>32.93</v>
+        <v>28.09</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ukrainian Premier League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Veres Rivne x Shakhtar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Veres Rivne</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T3" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Israeli National League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MS Kfar Kasem x Bnei Yehuda</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MS Kfar Kasem</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bnei Yehuda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>29.84</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.42</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.26</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -742,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.49</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -774,6 +786,88 @@
       </c>
       <c r="T4" t="n">
         <v>29.84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Czech 1 Liga</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zlin x Slavia Prague</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zlin</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slavia Prague</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>888</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T5" t="n">
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.33</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,6 +872,252 @@
       </c>
       <c r="T5" t="n">
         <v>36.73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Galatasaray x Kasimpasa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>3782</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais x Aarau</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aarau</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>German Bundesliga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dortmund x Werder Bremen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2037</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="T8" t="n">
+        <v>39.79</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
@@ -922,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.32</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1004,15 +1008,19 @@
       <c r="K7" t="n">
         <v>1.46</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1086,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,20 +581,6 @@
       <c r="P2" t="n">
         <v>564</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="T2" t="n">
-        <v>28.09</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,20 +653,6 @@
       <c r="P3" t="n">
         <v>351</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T3" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -773,20 +725,6 @@
       <c r="P4" t="n">
         <v>72</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>29.84</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,20 +797,6 @@
       <c r="P5" t="n">
         <v>888</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T5" t="n">
-        <v>36.73</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,20 +869,6 @@
       <c r="P6" t="n">
         <v>3782</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T6" t="n">
-        <v>32.93</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,20 +941,6 @@
       <c r="P7" t="n">
         <v>213</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>29.84</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1116,20 +1012,6 @@
       </c>
       <c r="P8" t="n">
         <v>2037</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T8" t="n">
-        <v>39.79</v>
       </c>
     </row>
   </sheetData>
